--- a/salon_forms/010_skin_and_hair_care_consultation_form--salon_forms.xlsx
+++ b/salon_forms/010_skin_and_hair_care_consultation_form--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1146,8 +1146,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal',_'value':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal', 'value': 'normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'oily',_'value':_'oily'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Oily', 'value': 'oily'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sensitive',_'value':_'sensitive'}</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sensitive', 'value': 'sensitive'}</t>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fine',_'value':_'fine'}</t>
+          <t>fine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fine', 'value': 'fine'}</t>
+          <t>Fine</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'thinning',_'value':_'thinning'}</t>
+          <t>thinning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Thinning', 'value': 'thinning'}</t>
+          <t>Thinning</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'damaged',_'value':_'damaged'}</t>
+          <t>damaged</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Damaged', 'value': 'damaged'}</t>
+          <t>Damaged</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'acetaminophen',_'value':_'acetaminophen'}</t>
+          <t>acetaminophen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Acetaminophen', 'value': 'acetaminophen'}</t>
+          <t>Acetaminophen</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'advil',_'value':_'advil'}</t>
+          <t>advil</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Advil', 'value': 'advil'}</t>
+          <t>Advil</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ibuprofen',_'value':_'ibuprofen'}</t>
+          <t>ibuprofen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Ibuprofen', 'value': 'ibuprofen'}</t>
+          <t>Ibuprofen</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'penicillin',_'value':_'penicillin'}</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Penicillin', 'value': 'penicillin'}</t>
+          <t>Penicillin</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'eczema',_'value':_'eczema'}</t>
+          <t>eczema</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Eczema', 'value': 'eczema'}</t>
+          <t>Eczema</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'latex',_'value':_'latex'}</t>
+          <t>latex</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Latex', 'value': 'latex'}</t>
+          <t>Latex</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'shampoo',_'value':_'shampoo'}</t>
+          <t>shampoo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Shampoo', 'value': 'shampoo'}</t>
+          <t>Shampoo</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'conditioner',_'value':_'conditioner'}</t>
+          <t>conditioner</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Conditioner', 'value': 'conditioner'}</t>
+          <t>Conditioner</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'serum',_'value':_'serum'}</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Serum', 'value': 'serum'}</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'moisturizer',_'value':_'moisturizer'}</t>
+          <t>moisturizer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Moisturizer', 'value': 'moisturizer'}</t>
+          <t>Moisturizer</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'exfoliant',_'value':_'exfoliant'}</t>
+          <t>exfoliant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Exfoliant', 'value': 'exfoliant'}</t>
+          <t>Exfoliant</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cleanser',_'value':_'cleanser'}</t>
+          <t>cleanser</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cleanser', 'value': 'cleanser'}</t>
+          <t>Cleanser</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'shampoo',_'value':_'shampoo'}</t>
+          <t>shampoo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Shampoo', 'value': 'shampoo'}</t>
+          <t>Shampoo</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'conditioner',_'value':_'conditioner'}</t>
+          <t>conditioner</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Conditioner', 'value': 'conditioner'}</t>
+          <t>Conditioner</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'serum',_'value':_'serum'}</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Serum', 'value': 'serum'}</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily', 'value': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily', 'value': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'text',_'value':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Text', 'value': 'text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
